--- a/AAII_Financials/Yearly/OBIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OBIO_YR_FIN.xlsx
@@ -2416,7 +2416,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>15200</v>
+        <v>31700</v>
       </c>
       <c r="E61" s="3">
         <v>16000</v>
@@ -2452,7 +2452,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19500</v>
+        <v>3100</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
